--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -460,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.41126</v>
+        <v>17.10679</v>
       </c>
       <c r="D2" t="n">
-        <v>17.50265</v>
+        <v>17.86898</v>
       </c>
       <c r="E2" t="n">
-        <v>17.4049</v>
+        <v>17.41136</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.56985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0512</v>
+        <v>0.0531</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92331</v>
+        <v>1.90726</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.74295</v>
+        <v>17.56352</v>
       </c>
       <c r="D3" t="n">
-        <v>17.38768</v>
+        <v>17.44998</v>
       </c>
       <c r="E3" t="n">
-        <v>17.55037</v>
+        <v>17.5477</v>
       </c>
       <c r="F3" t="n">
-        <v>44.10967</v>
+        <v>4466.081</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05426</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90068</v>
+        <v>1.9516</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>17.85553</v>
       </c>
       <c r="D4" t="n">
-        <v>17.26818</v>
+        <v>17.55668</v>
       </c>
       <c r="E4" t="n">
-        <v>17.52933</v>
+        <v>17.78848</v>
       </c>
       <c r="F4" t="n">
-        <v>45.20277</v>
+        <v>44.3952</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05154</v>
+        <v>0.05328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90245</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>17.63067</v>
       </c>
       <c r="D5" t="n">
-        <v>17.4339</v>
+        <v>17.22555</v>
       </c>
       <c r="E5" t="n">
-        <v>17.25448</v>
+        <v>17.51742</v>
       </c>
       <c r="F5" t="n">
-        <v>43.70495</v>
+        <v>44.77511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05205</v>
+        <v>0.05379</v>
       </c>
       <c r="H5" t="n">
-        <v>1.92828</v>
+        <v>1.90611</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.84138</v>
+        <v>17.66604</v>
       </c>
       <c r="D6" t="n">
-        <v>17.67938</v>
+        <v>17.24359</v>
       </c>
       <c r="E6" t="n">
-        <v>17.77962</v>
+        <v>17.41596</v>
       </c>
       <c r="F6" t="n">
-        <v>44.17934</v>
+        <v>44.49279</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05248</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.88619</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.8126</v>
+        <v>17.65201</v>
       </c>
       <c r="D7" t="n">
-        <v>17.53892</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>17.36982</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.53335</v>
       </c>
       <c r="F7" t="n">
-        <v>43.96503</v>
+        <v>44.49342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05283</v>
+        <v>0.05239</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86844</v>
+        <v>1.85785</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.80653</v>
+        <v>17.69148</v>
       </c>
       <c r="D8" t="n">
-        <v>17.45177</v>
+        <v>17.26635</v>
       </c>
       <c r="E8" t="n">
-        <v>17.69852</v>
+        <v>17.65374</v>
       </c>
       <c r="F8" t="n">
-        <v>44.4335</v>
+        <v>44.36579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05283</v>
+        <v>0.05403</v>
       </c>
       <c r="H8" t="n">
-        <v>1.90414</v>
+        <v>1.91531</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.70444</v>
+        <v>17.71365</v>
       </c>
       <c r="D9" t="n">
-        <v>17.33616</v>
+        <v>17.47491</v>
       </c>
       <c r="E9" t="n">
-        <v>17.63542</v>
+        <v>17.57958</v>
       </c>
       <c r="F9" t="n">
-        <v>45.45999</v>
+        <v>45.10707</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05356</v>
+        <v>0.05406</v>
       </c>
       <c r="H9" t="n">
-        <v>1.89047</v>
+        <v>1.8883</v>
       </c>
     </row>
     <row r="10">
@@ -663,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.57676</v>
+        <v>17.5294</v>
       </c>
       <c r="D10" t="n">
-        <v>17.25002</v>
+        <v>17.13062</v>
       </c>
       <c r="E10" t="n">
-        <v>17.60983</v>
+        <v>17.38389</v>
       </c>
       <c r="F10" t="n">
-        <v>43.76321</v>
+        <v>45.62896</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05338</v>
+        <v>0.05219</v>
       </c>
       <c r="H10" t="n">
-        <v>1.88832</v>
+        <v>1.92603</v>
       </c>
     </row>
     <row r="11">
@@ -705,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.63811</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1398</v>
+        <v>1.15679</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.62192</v>
       </c>
       <c r="D13" t="n">
-        <v>1.17158</v>
+        <v>1.1764</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.63688</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17221</v>
+        <v>1.15456</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.63475</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13361</v>
+        <v>1.17403</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.65168</v>
       </c>
       <c r="D16" t="n">
-        <v>1.15148</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.63602</v>
       </c>
       <c r="D17" t="n">
-        <v>1.16447</v>
+        <v>1.1869</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.6440399999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1.16412</v>
+        <v>1.14094</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.64606</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1463</v>
+        <v>1.17408</v>
       </c>
     </row>
     <row r="20">
@@ -809,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.62907</v>
       </c>
       <c r="D20" t="n">
-        <v>1.18991</v>
+        <v>1.17392</v>
       </c>
     </row>
     <row r="21">
@@ -869,28 +866,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.78088</v>
+        <v>0.77856</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08574</v>
+        <v>0.08386</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6555800000000001</v>
+        <v>0.64062</v>
       </c>
       <c r="F22" t="n">
-        <v>1.02782</v>
+        <v>0.9970599999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11471</v>
+        <v>0.11279</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00793</v>
+        <v>0.00795</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09813</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.13118</v>
+        <v>0.13448</v>
       </c>
     </row>
     <row r="23">
@@ -900,28 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.77906</v>
+        <v>0.7825299999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08561000000000001</v>
+        <v>0.08431</v>
       </c>
       <c r="E23" t="n">
-        <v>0.63362</v>
+        <v>0.64536</v>
       </c>
       <c r="F23" t="n">
-        <v>1.00837</v>
+        <v>1.00237</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11484</v>
+        <v>0.11422</v>
       </c>
       <c r="H23" t="n">
-        <v>0.007820000000000001</v>
+        <v>0.00772</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09854</v>
+        <v>0.09727</v>
       </c>
       <c r="J23" t="n">
-        <v>0.13185</v>
+        <v>0.13505</v>
       </c>
     </row>
     <row r="24">
@@ -931,28 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.78705</v>
+        <v>0.79832</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08595</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.63148</v>
+        <v>0.62585</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0179</v>
+        <v>1.00655</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11554</v>
+        <v>0.11638</v>
       </c>
       <c r="H24" t="n">
-        <v>0.007889999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.09818</v>
       </c>
       <c r="J24" t="n">
-        <v>0.13303</v>
+        <v>0.13215</v>
       </c>
     </row>
     <row r="25">
@@ -962,28 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.78828</v>
+        <v>0.7801</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08463</v>
+        <v>0.08280999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.64991</v>
+        <v>0.63525</v>
       </c>
       <c r="F25" t="n">
-        <v>1.00032</v>
+        <v>1.00758</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11227</v>
+        <v>0.11522</v>
       </c>
       <c r="H25" t="n">
-        <v>0.007939999999999999</v>
+        <v>0.00791</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09793</v>
+        <v>0.09828000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.13231</v>
+        <v>0.13303</v>
       </c>
     </row>
     <row r="26">
@@ -993,28 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.77207</v>
+        <v>0.76862</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08603</v>
+        <v>0.08458</v>
       </c>
       <c r="E26" t="n">
-        <v>0.65224</v>
+        <v>0.6398</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0237</v>
+        <v>0.98861</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11348</v>
+        <v>0.11436</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00805</v>
+        <v>0.00801</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09632</v>
+        <v>0.09723999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.13327</v>
+        <v>0.13249</v>
       </c>
     </row>
     <row r="27">
@@ -1024,28 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.78547</v>
+        <v>0.78516</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0861</v>
+        <v>0.08504</v>
       </c>
       <c r="E27" t="n">
-        <v>0.63919</v>
+        <v>0.63261</v>
       </c>
       <c r="F27" t="n">
-        <v>0.99057</v>
+        <v>0.99437</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11252</v>
+        <v>0.11433</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00813</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09694</v>
+        <v>0.09898</v>
       </c>
       <c r="J27" t="n">
-        <v>0.13302</v>
+        <v>0.13272</v>
       </c>
     </row>
     <row r="28">
@@ -1055,28 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.79922</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08475000000000001</v>
+        <v>0.08511000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.64649</v>
+        <v>0.63544</v>
       </c>
       <c r="F28" t="n">
-        <v>0.99826</v>
+        <v>0.99778</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11437</v>
+        <v>0.11532</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00787</v>
+        <v>0.00796</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09922</v>
+        <v>0.09662</v>
       </c>
       <c r="J28" t="n">
-        <v>0.13122</v>
+        <v>0.13375</v>
       </c>
     </row>
     <row r="29">
@@ -1086,28 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76976</v>
+        <v>0.7696499999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08548</v>
+        <v>0.08441</v>
       </c>
       <c r="E29" t="n">
-        <v>0.63425</v>
+        <v>0.63222</v>
       </c>
       <c r="F29" t="n">
-        <v>1.00101</v>
+        <v>0.99868</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11279</v>
+        <v>0.11683</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00804</v>
+        <v>0.008019999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09988</v>
+        <v>0.09539</v>
       </c>
       <c r="J29" t="n">
-        <v>0.13261</v>
+        <v>0.13177</v>
       </c>
     </row>
     <row r="30">
@@ -1117,28 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.79188</v>
+        <v>0.76581</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08404</v>
+        <v>0.08334</v>
       </c>
       <c r="E30" t="n">
-        <v>0.63142</v>
+        <v>0.63375</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0013</v>
+        <v>1.01109</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11337</v>
+        <v>0.11481</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00804</v>
+        <v>0.0078</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09676</v>
+        <v>0.09662</v>
       </c>
       <c r="J30" t="n">
-        <v>0.13334</v>
+        <v>0.13267</v>
       </c>
     </row>
   </sheetData>
